--- a/UnUn-Transmatch-es.xlsx
+++ b/UnUn-Transmatch-es.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="UnUn Calculator" sheetId="1" state="visible" r:id="rId3"/>
@@ -1209,383 +1209,383 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="12" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="12" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="17" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="17" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="17" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="18" fillId="10" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="11" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="18" fillId="11" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="10" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="18" fillId="10" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="19" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="13" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="13" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="13" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="19" fillId="13" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="19" fillId="13" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="19" fillId="13" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="19" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="19" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="19" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="20" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="20" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="20" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="20" fillId="12" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="171" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="172" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="18" fillId="11" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="19" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="19" fillId="13" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="19" fillId="13" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="174" fontId="19" fillId="13" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="174" fontId="19" fillId="13" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="10" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="10" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="14" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="22" fillId="14" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="13" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="13" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="19" fillId="13" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="19" fillId="13" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="19" fillId="13" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="171" fontId="19" fillId="13" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="19" fillId="13" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="172" fontId="19" fillId="13" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="19" fillId="13" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="19" fillId="13" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="175" fontId="19" fillId="13" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="175" fontId="19" fillId="13" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="13" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="13" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="175" fontId="4" fillId="13" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="175" fontId="4" fillId="13" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="4" fillId="13" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="4" fillId="13" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="14" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="23" fillId="14" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="15" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="19" fillId="15" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="19" fillId="13" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="19" fillId="13" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="19" fillId="13" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="19" fillId="13" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="15" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="19" fillId="15" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="16" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="16" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="17" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="18" fillId="17" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="25" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="25" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="17" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="18" fillId="17" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="13" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="13" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="175" fontId="10" fillId="13" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="175" fontId="10" fillId="13" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="10" fillId="13" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="172" fontId="10" fillId="13" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="26" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="26" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="28" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="28" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="29" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="29" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3991,7 +3991,7 @@
         <v>95</v>
       </c>
       <c r="C9" s="52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D9" s="53" t="s">
         <v>96</v>
@@ -4060,7 +4060,7 @@
       <c r="Z10" s="2"/>
       <c r="AA10" s="2"/>
     </row>
-    <row r="11" s="44" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" s="44" customFormat="true" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1"/>
       <c r="B11" s="47" t="s">
         <v>100</v>
@@ -4153,7 +4153,7 @@
       <c r="Z13" s="2"/>
       <c r="AA13" s="2"/>
     </row>
-    <row r="14" s="44" customFormat="true" ht="38.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" s="44" customFormat="true" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1"/>
       <c r="B14" s="46" t="s">
         <v>102</v>
@@ -4192,7 +4192,7 @@
       <c r="Z14" s="2"/>
       <c r="AA14" s="2"/>
     </row>
-    <row r="15" s="44" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" s="44" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1"/>
       <c r="B15" s="59" t="n">
         <v>1</v>
@@ -4207,7 +4207,7 @@
         <v>-12</v>
       </c>
       <c r="F15" s="59" t="str">
-        <f aca="false">IF(ROW()-15&lt;=$C$9,"YES","NO")</f>
+        <f aca="false">IF(ROW()-14&lt;=$C$9,"YES","NO")</f>
         <v>YES</v>
       </c>
       <c r="G15" s="62"/>
@@ -4232,7 +4232,7 @@
       <c r="Z15" s="2"/>
       <c r="AA15" s="2"/>
     </row>
-    <row r="16" s="44" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" s="44" customFormat="true" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1"/>
       <c r="B16" s="59" t="n">
         <v>2</v>
@@ -4247,8 +4247,8 @@
         <v>23</v>
       </c>
       <c r="F16" s="59" t="str">
-        <f aca="false">IF(ROW()-15&lt;=$C$9,"YES","NO")</f>
-        <v>YES</v>
+        <f aca="false">IF(ROW()-14&lt;=$C$9,"YES","NO")</f>
+        <v>NO</v>
       </c>
       <c r="G16" s="62"/>
       <c r="H16" s="49"/>
@@ -4272,7 +4272,7 @@
       <c r="Z16" s="2"/>
       <c r="AA16" s="2"/>
     </row>
-    <row r="17" s="44" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" s="44" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1"/>
       <c r="B17" s="59" t="n">
         <v>3</v>
@@ -4287,8 +4287,8 @@
         <v>10</v>
       </c>
       <c r="F17" s="59" t="str">
-        <f aca="false">IF(ROW()-15&lt;=$C$9,"YES","NO")</f>
-        <v>YES</v>
+        <f aca="false">IF(ROW()-14&lt;=$C$9,"YES","NO")</f>
+        <v>NO</v>
       </c>
       <c r="G17" s="62"/>
       <c r="H17" s="49"/>
@@ -4312,7 +4312,7 @@
       <c r="Z17" s="2"/>
       <c r="AA17" s="2"/>
     </row>
-    <row r="18" s="44" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" s="44" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1"/>
       <c r="B18" s="59" t="n">
         <v>4</v>
@@ -4321,7 +4321,7 @@
       <c r="D18" s="60"/>
       <c r="E18" s="61"/>
       <c r="F18" s="59" t="str">
-        <f aca="false">IF(ROW()-15&lt;=$C$9,"YES","NO")</f>
+        <f aca="false">IF(ROW()-14&lt;=$C$9,"YES","NO")</f>
         <v>NO</v>
       </c>
       <c r="G18" s="62"/>
@@ -4346,7 +4346,7 @@
       <c r="Z18" s="2"/>
       <c r="AA18" s="2"/>
     </row>
-    <row r="19" s="44" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" s="44" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1"/>
       <c r="B19" s="59" t="n">
         <v>5</v>
@@ -4355,7 +4355,7 @@
       <c r="D19" s="60"/>
       <c r="E19" s="61"/>
       <c r="F19" s="59" t="str">
-        <f aca="false">IF(ROW()-15&lt;=$C$9,"YES","NO")</f>
+        <f aca="false">IF(ROW()-14&lt;=$C$9,"YES","NO")</f>
         <v>NO</v>
       </c>
       <c r="G19" s="62"/>
@@ -4380,7 +4380,7 @@
       <c r="Z19" s="2"/>
       <c r="AA19" s="2"/>
     </row>
-    <row r="20" s="44" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" s="44" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1"/>
       <c r="B20" s="59" t="n">
         <v>6</v>
@@ -4389,7 +4389,7 @@
       <c r="D20" s="60"/>
       <c r="E20" s="61"/>
       <c r="F20" s="59" t="str">
-        <f aca="false">IF(ROW()-15&lt;=$C$9,"YES","NO")</f>
+        <f aca="false">IF(ROW()-14&lt;=$C$9,"YES","NO")</f>
         <v>NO</v>
       </c>
       <c r="G20" s="62"/>
@@ -4414,7 +4414,7 @@
       <c r="Z20" s="2"/>
       <c r="AA20" s="2"/>
     </row>
-    <row r="21" s="44" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" s="44" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1"/>
       <c r="B21" s="59" t="n">
         <v>7</v>
@@ -4423,7 +4423,7 @@
       <c r="D21" s="60"/>
       <c r="E21" s="61"/>
       <c r="F21" s="59" t="str">
-        <f aca="false">IF(ROW()-15&lt;=$C$9,"YES","NO")</f>
+        <f aca="false">IF(ROW()-14&lt;=$C$9,"YES","NO")</f>
         <v>NO</v>
       </c>
       <c r="G21" s="62"/>
@@ -4448,7 +4448,7 @@
       <c r="Z21" s="2"/>
       <c r="AA21" s="2"/>
     </row>
-    <row r="22" s="44" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" s="44" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1"/>
       <c r="B22" s="59" t="n">
         <v>8</v>
@@ -4457,7 +4457,7 @@
       <c r="D22" s="60"/>
       <c r="E22" s="61"/>
       <c r="F22" s="59" t="str">
-        <f aca="false">IF(ROW()-15&lt;=$C$9,"YES","NO")</f>
+        <f aca="false">IF(ROW()-14&lt;=$C$9,"YES","NO")</f>
         <v>NO</v>
       </c>
       <c r="G22" s="62"/>
@@ -4482,7 +4482,7 @@
       <c r="Z22" s="2"/>
       <c r="AA22" s="2"/>
     </row>
-    <row r="23" s="44" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" s="44" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1"/>
       <c r="B23" s="59" t="n">
         <v>9</v>
@@ -4491,7 +4491,7 @@
       <c r="D23" s="60"/>
       <c r="E23" s="61"/>
       <c r="F23" s="59" t="str">
-        <f aca="false">IF(ROW()-15&lt;=$C$9,"YES","NO")</f>
+        <f aca="false">IF(ROW()-14&lt;=$C$9,"YES","NO")</f>
         <v>NO</v>
       </c>
       <c r="G23" s="62"/>
@@ -4516,7 +4516,7 @@
       <c r="Z23" s="2"/>
       <c r="AA23" s="2"/>
     </row>
-    <row r="24" s="44" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" s="44" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1"/>
       <c r="B24" s="59" t="n">
         <v>10</v>
@@ -4525,7 +4525,7 @@
       <c r="D24" s="60"/>
       <c r="E24" s="61"/>
       <c r="F24" s="59" t="str">
-        <f aca="false">IF(ROW()-15&lt;=$C$9,"YES","NO")</f>
+        <f aca="false">IF(ROW()-14&lt;=$C$9,"YES","NO")</f>
         <v>NO</v>
       </c>
       <c r="G24" s="62"/>
@@ -4550,7 +4550,7 @@
       <c r="Z24" s="2"/>
       <c r="AA24" s="2"/>
     </row>
-    <row r="25" s="44" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" s="44" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1"/>
       <c r="B25" s="59" t="n">
         <v>11</v>
@@ -4559,7 +4559,7 @@
       <c r="D25" s="60"/>
       <c r="E25" s="61"/>
       <c r="F25" s="59" t="str">
-        <f aca="false">IF(ROW()-15&lt;=$C$9,"YES","NO")</f>
+        <f aca="false">IF(ROW()-14&lt;=$C$9,"YES","NO")</f>
         <v>NO</v>
       </c>
       <c r="G25" s="62"/>
@@ -4735,7 +4735,7 @@
       <c r="Z30" s="2"/>
       <c r="AA30" s="2"/>
     </row>
-    <row r="31" s="44" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" s="44" customFormat="true" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1"/>
       <c r="B31" s="47" t="s">
         <v>110</v>
@@ -4771,7 +4771,7 @@
       <c r="Z31" s="2"/>
       <c r="AA31" s="2"/>
     </row>
-    <row r="32" s="44" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" s="44" customFormat="true" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1"/>
       <c r="B32" s="47" t="s">
         <v>111</v>
@@ -4807,7 +4807,7 @@
       <c r="Z32" s="2"/>
       <c r="AA32" s="2"/>
     </row>
-    <row r="33" s="44" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" s="44" customFormat="true" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1"/>
       <c r="B33" s="47" t="s">
         <v>112</v>
@@ -4843,14 +4843,14 @@
       <c r="Z33" s="2"/>
       <c r="AA33" s="2"/>
     </row>
-    <row r="34" s="44" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" s="44" customFormat="true" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1"/>
       <c r="B34" s="47" t="s">
         <v>114</v>
       </c>
       <c r="C34" s="53" t="n">
         <f aca="false">C9</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D34" s="65" t="s">
         <v>96</v>
@@ -4879,7 +4879,7 @@
       <c r="Z34" s="2"/>
       <c r="AA34" s="2"/>
     </row>
-    <row r="35" s="44" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" s="44" customFormat="true" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1"/>
       <c r="B35" s="47" t="s">
         <v>115</v>
@@ -4915,7 +4915,7 @@
       <c r="Z35" s="2"/>
       <c r="AA35" s="2"/>
     </row>
-    <row r="36" s="44" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" s="44" customFormat="true" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1"/>
       <c r="B36" s="47" t="s">
         <v>116</v>
@@ -4951,7 +4951,7 @@
       <c r="Z36" s="2"/>
       <c r="AA36" s="2"/>
     </row>
-    <row r="37" s="44" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" s="44" customFormat="true" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1"/>
       <c r="B37" s="47" t="s">
         <v>117</v>
@@ -5045,7 +5045,7 @@
       <c r="Z39" s="2"/>
       <c r="AA39" s="2"/>
     </row>
-    <row r="40" s="44" customFormat="true" ht="38.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" s="44" customFormat="true" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="1"/>
       <c r="B40" s="46" t="s">
         <v>102</v>
@@ -5112,7 +5112,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="41" s="44" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" s="44" customFormat="true" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="1"/>
       <c r="B41" s="70" t="n">
         <v>1</v>
@@ -5196,7 +5196,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" s="44" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" s="44" customFormat="true" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="1"/>
       <c r="B42" s="70" t="n">
         <v>2</v>
@@ -5237,33 +5237,33 @@
         <f aca="false">IF(D42&lt;&gt;"",G132,"—")</f>
         <v>—</v>
       </c>
-      <c r="L42" s="77" t="n">
+      <c r="L42" s="77" t="str">
         <f aca="false">IF(D42&lt;&gt;"",H132,"—")</f>
-        <v>654.375820757693</v>
+        <v>—</v>
       </c>
       <c r="M42" s="76" t="str">
         <f aca="false">IF(D42&lt;&gt;"",I132,"—")</f>
         <v>—</v>
       </c>
-      <c r="N42" s="77" t="n">
+      <c r="N42" s="77" t="str">
         <f aca="false">IF(D42&lt;&gt;"",J132,"—")</f>
-        <v>68.9846172141929</v>
+        <v>—</v>
       </c>
       <c r="O42" s="78" t="str">
         <f aca="false">IF(ISNUMBER(K42),ROUND(K42*1000,0),"—")</f>
         <v>—</v>
       </c>
-      <c r="P42" s="78" t="n">
+      <c r="P42" s="78" t="str">
         <f aca="false">IF(ISNUMBER(L42),LOOKUP(2,1/(ABS($AA$41:$AA$161-L42)=MIN(ABS($AA$41:$AA$161-L42))),$AA$41:$AA$161),"—")</f>
-        <v>680</v>
+        <v>—</v>
       </c>
       <c r="Q42" s="78" t="str">
         <f aca="false">IF(ISNUMBER(M42),ROUND(M42*1000,0),"—")</f>
         <v>—</v>
       </c>
-      <c r="R42" s="78" t="n">
+      <c r="R42" s="78" t="str">
         <f aca="false">IF(ISNUMBER(N42),LOOKUP(2,1/(ABS($AA$41:$AA$161-N42)=MIN(ABS($AA$41:$AA$161-N42))),$AA$41:$AA$161),"—")</f>
-        <v>68</v>
+        <v>—</v>
       </c>
       <c r="S42" s="76" t="n">
         <f aca="false">IF(D42="","—",IFERROR((1+ABS(0.05*E16*$C$6/D16)/SQRT(4*$C$6^2+(0.05*E16*$C$6/D16)^2))/(1-ABS(0.05*E16*$C$6/D16)/SQRT(4*$C$6^2+(0.05*E16*$C$6/D16)^2)),"—"))</f>
@@ -5280,7 +5280,7 @@
         <v>1.1</v>
       </c>
     </row>
-    <row r="43" s="44" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" s="44" customFormat="true" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="1"/>
       <c r="B43" s="70" t="n">
         <v>3</v>
@@ -5321,33 +5321,33 @@
         <f aca="false">IF(D43&lt;&gt;"",G133,"—")</f>
         <v>—</v>
       </c>
-      <c r="L43" s="77" t="n">
+      <c r="L43" s="77" t="str">
         <f aca="false">IF(D43&lt;&gt;"",H133,"—")</f>
-        <v>511.569459938235</v>
+        <v>—</v>
       </c>
       <c r="M43" s="76" t="str">
         <f aca="false">IF(D43&lt;&gt;"",I133,"—")</f>
         <v>—</v>
       </c>
-      <c r="N43" s="77" t="n">
+      <c r="N43" s="77" t="str">
         <f aca="false">IF(D43&lt;&gt;"",J133,"—")</f>
-        <v>24.0738569382699</v>
+        <v>—</v>
       </c>
       <c r="O43" s="78" t="str">
         <f aca="false">IF(ISNUMBER(K43),ROUND(K43*1000,0),"—")</f>
         <v>—</v>
       </c>
-      <c r="P43" s="78" t="n">
+      <c r="P43" s="78" t="str">
         <f aca="false">IF(ISNUMBER(L43),LOOKUP(2,1/(ABS($AA$41:$AA$161-L43)=MIN(ABS($AA$41:$AA$161-L43))),$AA$41:$AA$161),"—")</f>
-        <v>510</v>
+        <v>—</v>
       </c>
       <c r="Q43" s="78" t="str">
         <f aca="false">IF(ISNUMBER(M43),ROUND(M43*1000,0),"—")</f>
         <v>—</v>
       </c>
-      <c r="R43" s="78" t="n">
+      <c r="R43" s="78" t="str">
         <f aca="false">IF(ISNUMBER(N43),LOOKUP(2,1/(ABS($AA$41:$AA$161-N43)=MIN(ABS($AA$41:$AA$161-N43))),$AA$41:$AA$161),"—")</f>
-        <v>24</v>
+        <v>—</v>
       </c>
       <c r="S43" s="76" t="n">
         <f aca="false">IF(D43="","—",IFERROR((1+ABS(0.05*E17*$C$6/D17)/SQRT(4*$C$6^2+(0.05*E17*$C$6/D17)^2))/(1-ABS(0.05*E17*$C$6/D17)/SQRT(4*$C$6^2+(0.05*E17*$C$6/D17)^2)),"—"))</f>
@@ -5364,7 +5364,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="44" s="44" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" s="44" customFormat="true" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="1"/>
       <c r="B44" s="70" t="n">
         <v>4</v>
@@ -5448,7 +5448,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="45" s="44" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" s="44" customFormat="true" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="1"/>
       <c r="B45" s="70" t="n">
         <v>5</v>
@@ -5532,7 +5532,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="46" s="44" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" s="44" customFormat="true" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="1"/>
       <c r="B46" s="70" t="n">
         <v>6</v>
@@ -5616,7 +5616,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="47" s="44" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" s="44" customFormat="true" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="1"/>
       <c r="B47" s="70" t="n">
         <v>7</v>
@@ -5700,7 +5700,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="48" s="44" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" s="44" customFormat="true" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="1"/>
       <c r="B48" s="70" t="n">
         <v>8</v>
@@ -5784,7 +5784,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="49" s="44" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" s="44" customFormat="true" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="1"/>
       <c r="B49" s="70" t="n">
         <v>9</v>
@@ -5868,7 +5868,7 @@
         <v>2.2</v>
       </c>
     </row>
-    <row r="50" s="44" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" s="44" customFormat="true" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="1"/>
       <c r="B50" s="70" t="n">
         <v>10</v>
@@ -5952,7 +5952,7 @@
         <v>2.4</v>
       </c>
     </row>
-    <row r="51" s="44" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" s="44" customFormat="true" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="1"/>
       <c r="B51" s="70" t="n">
         <v>11</v>
@@ -6197,7 +6197,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="57" s="44" customFormat="true" ht="75.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" s="44" customFormat="true" ht="73.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="1"/>
       <c r="B57" s="46" t="s">
         <v>102</v>
@@ -6244,7 +6244,7 @@
         <v>4.7</v>
       </c>
     </row>
-    <row r="58" s="44" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" s="44" customFormat="true" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="1"/>
       <c r="B58" s="53" t="n">
         <v>1</v>
@@ -6298,7 +6298,7 @@
         <v>5.1</v>
       </c>
     </row>
-    <row r="59" s="44" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" s="44" customFormat="true" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="1"/>
       <c r="B59" s="53" t="n">
         <v>2</v>
@@ -6352,7 +6352,7 @@
         <v>5.6</v>
       </c>
     </row>
-    <row r="60" s="44" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" s="44" customFormat="true" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="1"/>
       <c r="B60" s="53" t="n">
         <v>3</v>
@@ -6406,7 +6406,7 @@
         <v>6.2</v>
       </c>
     </row>
-    <row r="61" s="44" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" s="44" customFormat="true" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="1"/>
       <c r="B61" s="53" t="n">
         <v>4</v>
@@ -6460,7 +6460,7 @@
         <v>6.8</v>
       </c>
     </row>
-    <row r="62" s="44" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" s="44" customFormat="true" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="1"/>
       <c r="B62" s="53" t="n">
         <v>5</v>
@@ -6514,7 +6514,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="63" s="44" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" s="44" customFormat="true" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="1"/>
       <c r="B63" s="53" t="n">
         <v>6</v>
@@ -6568,7 +6568,7 @@
         <v>8.2</v>
       </c>
     </row>
-    <row r="64" s="44" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" s="44" customFormat="true" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="1"/>
       <c r="B64" s="53" t="n">
         <v>7</v>
@@ -6622,7 +6622,7 @@
         <v>9.1</v>
       </c>
     </row>
-    <row r="65" s="44" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" s="44" customFormat="true" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="1"/>
       <c r="B65" s="53" t="n">
         <v>8</v>
@@ -6676,7 +6676,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="66" s="44" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" s="44" customFormat="true" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="1"/>
       <c r="B66" s="53" t="n">
         <v>9</v>
@@ -6730,7 +6730,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="67" s="44" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" s="44" customFormat="true" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="1"/>
       <c r="B67" s="53" t="n">
         <v>10</v>
@@ -6784,7 +6784,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="68" s="44" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" s="44" customFormat="true" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="1"/>
       <c r="B68" s="53" t="n">
         <v>11</v>
@@ -7072,7 +7072,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="76" s="44" customFormat="true" ht="38.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" s="44" customFormat="true" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="1"/>
       <c r="B76" s="46" t="s">
         <v>102</v>
@@ -7119,7 +7119,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="77" s="44" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" s="44" customFormat="true" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="1"/>
       <c r="B77" s="70" t="n">
         <v>1</v>
@@ -7173,7 +7173,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="78" s="44" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" s="44" customFormat="true" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="1"/>
       <c r="B78" s="70" t="n">
         <v>2</v>
@@ -7227,7 +7227,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="79" s="44" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" s="44" customFormat="true" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="1"/>
       <c r="B79" s="70" t="n">
         <v>3</v>
@@ -7281,7 +7281,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="80" s="44" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" s="44" customFormat="true" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="1"/>
       <c r="B80" s="70" t="n">
         <v>4</v>
@@ -7335,7 +7335,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="81" s="44" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" s="44" customFormat="true" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="1"/>
       <c r="B81" s="70" t="n">
         <v>5</v>
@@ -7389,7 +7389,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="82" s="44" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" s="44" customFormat="true" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="1"/>
       <c r="B82" s="70" t="n">
         <v>6</v>
@@ -7443,7 +7443,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="83" s="44" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" s="44" customFormat="true" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="1"/>
       <c r="B83" s="70" t="n">
         <v>7</v>
@@ -7497,7 +7497,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="84" s="44" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" s="44" customFormat="true" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="1"/>
       <c r="B84" s="70" t="n">
         <v>8</v>
@@ -7551,7 +7551,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="85" s="44" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" s="44" customFormat="true" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="1"/>
       <c r="B85" s="70" t="n">
         <v>9</v>
@@ -7605,7 +7605,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="86" s="44" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" s="44" customFormat="true" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="1"/>
       <c r="B86" s="70" t="n">
         <v>10</v>
@@ -7659,7 +7659,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="87" s="44" customFormat="true" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="87" s="44" customFormat="true" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="1"/>
       <c r="B87" s="70" t="n">
         <v>11</v>
@@ -9179,7 +9179,7 @@
         <v>4700</v>
       </c>
     </row>
-    <row r="130" s="44" customFormat="true" ht="26.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="130" s="44" customFormat="true" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="1"/>
       <c r="B130" s="88" t="s">
         <v>102</v>
@@ -9310,17 +9310,17 @@
         <f aca="false">IFERROR(IF(AND(F16="YES",ISNUMBER(D78),D78&gt;0,ISNUMBER(D16),D16&gt;0),IF(($C$6*IF(ISNUMBER(E16),E16,0)/D16)&lt;0,ABS($C$6*IF(ISNUMBER(E16),E16,0)/D16)/(2*PI()*C16*1000000)*1000000,"—"),"—"),"—")</f>
         <v>—</v>
       </c>
-      <c r="H132" s="90" t="n">
+      <c r="H132" s="90" t="str">
         <f aca="false">IFERROR(IF(AND(F16="YES",ISNUMBER(D78),D78&gt;0,ISNUMBER(D16),D16&gt;0),IF(($C$6*IF(ISNUMBER(E16),E16,0)/D16)&gt;0,1/((2*PI()*C16*1000000)*ABS($C$6*IF(ISNUMBER(E16),E16,0)/D16))*1000000000000,"—"),"—"),"—")</f>
-        <v>654.375820757693</v>
+        <v>—</v>
       </c>
       <c r="I132" s="91" t="str">
         <f aca="false">IFERROR(IF(AND(F16="YES",ISNUMBER(D78),D78&gt;0,ISNUMBER(D16),D16&gt;0),IF((D16*IF(ISNUMBER(E16),E16,0)/($C$6*(D16^2+IF(ISNUMBER(E16),E16,0)^2)))&lt;0,-1/((2*PI()*C16*1000000)*(D16*IF(ISNUMBER(E16),E16,0)/($C$6*(D16^2+IF(ISNUMBER(E16),E16,0)^2))))*1000000,"—"),"—"),"—")</f>
         <v>—</v>
       </c>
-      <c r="J132" s="90" t="n">
+      <c r="J132" s="90" t="str">
         <f aca="false">IFERROR(IF(AND(F16="YES",ISNUMBER(D78),D78&gt;0,ISNUMBER(D16),D16&gt;0),IF((D16*IF(ISNUMBER(E16),E16,0)/($C$6*(D16^2+IF(ISNUMBER(E16),E16,0)^2)))&gt;0,(D16*IF(ISNUMBER(E16),E16,0)/($C$6*(D16^2+IF(ISNUMBER(E16),E16,0)^2)))/(2*PI()*C16*1000000)*1000000000000,"—"),"—"),"—")</f>
-        <v>68.9846172141929</v>
+        <v>—</v>
       </c>
       <c r="K132" s="2"/>
       <c r="L132" s="2"/>
@@ -9367,17 +9367,17 @@
         <f aca="false">IFERROR(IF(AND(F17="YES",ISNUMBER(D79),D79&gt;0,ISNUMBER(D17),D17&gt;0),IF(($C$6*IF(ISNUMBER(E17),E17,0)/D17)&lt;0,ABS($C$6*IF(ISNUMBER(E17),E17,0)/D17)/(2*PI()*C17*1000000)*1000000,"—"),"—"),"—")</f>
         <v>—</v>
       </c>
-      <c r="H133" s="90" t="n">
+      <c r="H133" s="90" t="str">
         <f aca="false">IFERROR(IF(AND(F17="YES",ISNUMBER(D79),D79&gt;0,ISNUMBER(D17),D17&gt;0),IF(($C$6*IF(ISNUMBER(E17),E17,0)/D17)&gt;0,1/((2*PI()*C17*1000000)*ABS($C$6*IF(ISNUMBER(E17),E17,0)/D17))*1000000000000,"—"),"—"),"—")</f>
-        <v>511.569459938235</v>
+        <v>—</v>
       </c>
       <c r="I133" s="91" t="str">
         <f aca="false">IFERROR(IF(AND(F17="YES",ISNUMBER(D79),D79&gt;0,ISNUMBER(D17),D17&gt;0),IF((D17*IF(ISNUMBER(E17),E17,0)/($C$6*(D17^2+IF(ISNUMBER(E17),E17,0)^2)))&lt;0,-1/((2*PI()*C17*1000000)*(D17*IF(ISNUMBER(E17),E17,0)/($C$6*(D17^2+IF(ISNUMBER(E17),E17,0)^2))))*1000000,"—"),"—"),"—")</f>
         <v>—</v>
       </c>
-      <c r="J133" s="90" t="n">
+      <c r="J133" s="90" t="str">
         <f aca="false">IFERROR(IF(AND(F17="YES",ISNUMBER(D79),D79&gt;0,ISNUMBER(D17),D17&gt;0),IF((D17*IF(ISNUMBER(E17),E17,0)/($C$6*(D17^2+IF(ISNUMBER(E17),E17,0)^2)))&gt;0,(D17*IF(ISNUMBER(E17),E17,0)/($C$6*(D17^2+IF(ISNUMBER(E17),E17,0)^2)))/(2*PI()*C17*1000000)*1000000000000,"—"),"—"),"—")</f>
-        <v>24.0738569382699</v>
+        <v>—</v>
       </c>
       <c r="K133" s="2"/>
       <c r="L133" s="2"/>

--- a/UnUn-Transmatch-es.xlsx
+++ b/UnUn-Transmatch-es.xlsx
@@ -40,7 +40,7 @@
     <t xml:space="preserve">Frecuencia de Operación</t>
   </si>
   <si>
-    <t xml:space="preserve">MHz  [auto ↑]</t>
+    <t xml:space="preserve">MHz</t>
   </si>
   <si>
     <t xml:space="preserve">Impedancia de Entrada Objetivo (Real, Rin)</t>
@@ -1893,7 +1893,6 @@
         <v>3</v>
       </c>
       <c r="C5" s="8" t="n">
-        <f aca="false">IFERROR(INDEX(#REF!,MATCH(#REF!,#REF!,0)),7.1)</f>
         <v>7.1</v>
       </c>
       <c r="D5" s="9" t="s">
@@ -3954,7 +3953,7 @@
         <v>93</v>
       </c>
       <c r="C8" s="48" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="D8" s="49" t="s">
         <v>16</v>
@@ -3991,7 +3990,7 @@
         <v>95</v>
       </c>
       <c r="C9" s="52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D9" s="53" t="s">
         <v>96</v>
@@ -4028,11 +4027,11 @@
         <v>98</v>
       </c>
       <c r="C10" s="48" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D10" s="54" t="n">
         <f aca="false">IFERROR(MAX(CEILING(5/MIN(D58:D68),1),CEILING((5*C116*(C105/25.4)+SQRT(C116*(25*C116*(C105/25.4)^2+C112^2*(9*C112-10*(C105/25.4)+10*(C7/25.4)))))/(C112^2*MAX(D58:D68)),1)),5)</f>
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E10" s="55" t="s">
         <v>99</v>
@@ -4192,7 +4191,7 @@
       <c r="Z14" s="2"/>
       <c r="AA14" s="2"/>
     </row>
-    <row r="15" s="44" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" s="44" customFormat="true" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1"/>
       <c r="B15" s="59" t="n">
         <v>1</v>
@@ -4201,10 +4200,10 @@
         <v>7.15</v>
       </c>
       <c r="D15" s="60" t="n">
-        <v>75</v>
+        <v>408</v>
       </c>
       <c r="E15" s="61" t="n">
-        <v>-12</v>
+        <v>93.2</v>
       </c>
       <c r="F15" s="59" t="str">
         <f aca="false">IF(ROW()-14&lt;=$C$9,"YES","NO")</f>
@@ -4241,14 +4240,14 @@
         <v>14.17</v>
       </c>
       <c r="D16" s="60" t="n">
-        <v>67</v>
+        <v>619.9</v>
       </c>
       <c r="E16" s="61" t="n">
-        <v>23</v>
+        <v>296.1</v>
       </c>
       <c r="F16" s="59" t="str">
         <f aca="false">IF(ROW()-14&lt;=$C$9,"YES","NO")</f>
-        <v>NO</v>
+        <v>YES</v>
       </c>
       <c r="G16" s="62"/>
       <c r="H16" s="49"/>
@@ -4272,20 +4271,14 @@
       <c r="Z16" s="2"/>
       <c r="AA16" s="2"/>
     </row>
-    <row r="17" s="44" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" s="44" customFormat="true" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1"/>
       <c r="B17" s="59" t="n">
         <v>3</v>
       </c>
-      <c r="C17" s="48" t="n">
-        <v>28</v>
-      </c>
-      <c r="D17" s="60" t="n">
-        <v>45</v>
-      </c>
-      <c r="E17" s="61" t="n">
-        <v>10</v>
-      </c>
+      <c r="C17" s="48"/>
+      <c r="D17" s="60"/>
+      <c r="E17" s="61"/>
       <c r="F17" s="59" t="str">
         <f aca="false">IF(ROW()-14&lt;=$C$9,"YES","NO")</f>
         <v>NO</v>
@@ -4312,7 +4305,7 @@
       <c r="Z17" s="2"/>
       <c r="AA17" s="2"/>
     </row>
-    <row r="18" s="44" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" s="44" customFormat="true" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1"/>
       <c r="B18" s="59" t="n">
         <v>4</v>
@@ -4346,7 +4339,7 @@
       <c r="Z18" s="2"/>
       <c r="AA18" s="2"/>
     </row>
-    <row r="19" s="44" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" s="44" customFormat="true" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1"/>
       <c r="B19" s="59" t="n">
         <v>5</v>
@@ -4380,7 +4373,7 @@
       <c r="Z19" s="2"/>
       <c r="AA19" s="2"/>
     </row>
-    <row r="20" s="44" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" s="44" customFormat="true" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1"/>
       <c r="B20" s="59" t="n">
         <v>6</v>
@@ -4414,7 +4407,7 @@
       <c r="Z20" s="2"/>
       <c r="AA20" s="2"/>
     </row>
-    <row r="21" s="44" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" s="44" customFormat="true" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1"/>
       <c r="B21" s="59" t="n">
         <v>7</v>
@@ -4448,7 +4441,7 @@
       <c r="Z21" s="2"/>
       <c r="AA21" s="2"/>
     </row>
-    <row r="22" s="44" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" s="44" customFormat="true" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1"/>
       <c r="B22" s="59" t="n">
         <v>8</v>
@@ -4482,7 +4475,7 @@
       <c r="Z22" s="2"/>
       <c r="AA22" s="2"/>
     </row>
-    <row r="23" s="44" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" s="44" customFormat="true" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1"/>
       <c r="B23" s="59" t="n">
         <v>9</v>
@@ -4516,7 +4509,7 @@
       <c r="Z23" s="2"/>
       <c r="AA23" s="2"/>
     </row>
-    <row r="24" s="44" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" s="44" customFormat="true" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1"/>
       <c r="B24" s="59" t="n">
         <v>10</v>
@@ -4550,7 +4543,7 @@
       <c r="Z24" s="2"/>
       <c r="AA24" s="2"/>
     </row>
-    <row r="25" s="44" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" s="44" customFormat="true" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1"/>
       <c r="B25" s="59" t="n">
         <v>11</v>
@@ -4814,7 +4807,7 @@
       </c>
       <c r="C33" s="53" t="n">
         <f aca="false">C10</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D33" s="65" t="s">
         <v>113</v>
@@ -4850,7 +4843,7 @@
       </c>
       <c r="C34" s="53" t="n">
         <f aca="false">C9</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D34" s="65" t="s">
         <v>96</v>
@@ -4886,7 +4879,7 @@
       </c>
       <c r="C35" s="66" t="n">
         <f aca="false">I70</f>
-        <v>1762.43347866387</v>
+        <v>4121.76956150981</v>
       </c>
       <c r="D35" s="65" t="s">
         <v>16</v>
@@ -4922,7 +4915,7 @@
       </c>
       <c r="C36" s="67" t="n">
         <f aca="false">IFERROR(C114,"—")</f>
-        <v>5.19056793432736</v>
+        <v>20.8009357946279</v>
       </c>
       <c r="D36" s="65" t="s">
         <v>52</v>
@@ -5123,67 +5116,67 @@
       </c>
       <c r="D41" s="71" t="n">
         <f aca="false">D77</f>
-        <v>75.953933407033</v>
+        <v>418.509545888741</v>
       </c>
       <c r="E41" s="72" t="n">
         <f aca="false">E77</f>
-        <v>-9.09027692082232</v>
+        <v>12.8673751381485</v>
       </c>
       <c r="F41" s="73" t="n">
         <f aca="false">D58</f>
-        <v>1.22474487139159</v>
+        <v>2.85657137141714</v>
       </c>
       <c r="G41" s="54" t="n">
         <f aca="false">E58</f>
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="H41" s="74" t="n">
         <f aca="false">F77</f>
-        <v>1.173311183411</v>
+        <v>1.25600695982198</v>
       </c>
       <c r="I41" s="75" t="n">
         <f aca="false">G77</f>
-        <v>21.9659065411731</v>
+        <v>18.9017732577814</v>
       </c>
       <c r="J41" s="74" t="n">
         <f aca="false">I77</f>
-        <v>0.635930047694754</v>
-      </c>
-      <c r="K41" s="76" t="n">
+        <v>1.28772365686098</v>
+      </c>
+      <c r="K41" s="76" t="str">
         <f aca="false">IF(D41&lt;&gt;"",G131,"—")</f>
-        <v>0.178075460802121</v>
-      </c>
-      <c r="L41" s="77" t="str">
+        <v>—</v>
+      </c>
+      <c r="L41" s="77" t="n">
         <f aca="false">IF(D41&lt;&gt;"",H131,"—")</f>
-        <v>—</v>
-      </c>
-      <c r="M41" s="76" t="n">
+        <v>1948.89452809188</v>
+      </c>
+      <c r="M41" s="76" t="str">
         <f aca="false">IF(D41&lt;&gt;"",I131,"—")</f>
-        <v>7.13414814838496</v>
-      </c>
-      <c r="N41" s="77" t="str">
+        <v>—</v>
+      </c>
+      <c r="N41" s="77" t="n">
         <f aca="false">IF(D41&lt;&gt;"",J131,"—")</f>
-        <v>—</v>
-      </c>
-      <c r="O41" s="78" t="n">
+        <v>96.6516837527188</v>
+      </c>
+      <c r="O41" s="78" t="str">
         <f aca="false">IF(ISNUMBER(K41),ROUND(K41*1000,0),"—")</f>
-        <v>178</v>
-      </c>
-      <c r="P41" s="78" t="str">
+        <v>—</v>
+      </c>
+      <c r="P41" s="78" t="n">
         <f aca="false">IF(ISNUMBER(L41),LOOKUP(2,1/(ABS($AA$41:$AA$161-L41)=MIN(ABS($AA$41:$AA$161-L41))),$AA$41:$AA$161),"—")</f>
-        <v>—</v>
-      </c>
-      <c r="Q41" s="78" t="n">
+        <v>2000</v>
+      </c>
+      <c r="Q41" s="78" t="str">
         <f aca="false">IF(ISNUMBER(M41),ROUND(M41*1000,0),"—")</f>
-        <v>7134</v>
-      </c>
-      <c r="R41" s="78" t="str">
+        <v>—</v>
+      </c>
+      <c r="R41" s="78" t="n">
         <f aca="false">IF(ISNUMBER(N41),LOOKUP(2,1/(ABS($AA$41:$AA$161-N41)=MIN(ABS($AA$41:$AA$161-N41))),$AA$41:$AA$161),"—")</f>
-        <v>—</v>
+        <v>100</v>
       </c>
       <c r="S41" s="76" t="n">
         <f aca="false">IF(D41="","—",IFERROR((1+ABS(0.05*E15*$C$6/D15)/SQRT(4*$C$6^2+(0.05*E15*$C$6/D15)^2))/(1-ABS(0.05*E15*$C$6/D15)/SQRT(4*$C$6^2+(0.05*E15*$C$6/D15)^2)),"—"))</f>
-        <v>1.00803206399974</v>
+        <v>1.01148698098703</v>
       </c>
       <c r="T41" s="2"/>
       <c r="U41" s="2"/>
@@ -5207,67 +5200,67 @@
       </c>
       <c r="D42" s="71" t="n">
         <f aca="false">D78</f>
-        <v>70.8378429936994</v>
+        <v>686.987059557893</v>
       </c>
       <c r="E42" s="72" t="n">
         <f aca="false">E78</f>
-        <v>18.9465046895091</v>
+        <v>25.5318321834818</v>
       </c>
       <c r="F42" s="73" t="n">
         <f aca="false">D59</f>
-        <v>1.15758369027902</v>
+        <v>3.52107937996291</v>
       </c>
       <c r="G42" s="54" t="n">
         <f aca="false">E59</f>
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="H42" s="74" t="n">
         <f aca="false">F78</f>
-        <v>1.4072254081761</v>
+        <v>1.60516982405877</v>
       </c>
       <c r="I42" s="75" t="n">
         <f aca="false">G78</f>
-        <v>15.4336378287394</v>
+        <v>12.6791754929366</v>
       </c>
       <c r="J42" s="74" t="n">
         <f aca="false">I78</f>
-        <v>2.86177982147687</v>
+        <v>5.39613058204676</v>
       </c>
       <c r="K42" s="76" t="str">
         <f aca="false">IF(D42&lt;&gt;"",G132,"—")</f>
         <v>—</v>
       </c>
-      <c r="L42" s="77" t="str">
+      <c r="L42" s="77" t="n">
         <f aca="false">IF(D42&lt;&gt;"",H132,"—")</f>
-        <v>—</v>
+        <v>470.287576283575</v>
       </c>
       <c r="M42" s="76" t="str">
         <f aca="false">IF(D42&lt;&gt;"",I132,"—")</f>
         <v>—</v>
       </c>
-      <c r="N42" s="77" t="str">
+      <c r="N42" s="77" t="n">
         <f aca="false">IF(D42&lt;&gt;"",J132,"—")</f>
-        <v>—</v>
+        <v>87.3661519744635</v>
       </c>
       <c r="O42" s="78" t="str">
         <f aca="false">IF(ISNUMBER(K42),ROUND(K42*1000,0),"—")</f>
         <v>—</v>
       </c>
-      <c r="P42" s="78" t="str">
+      <c r="P42" s="78" t="n">
         <f aca="false">IF(ISNUMBER(L42),LOOKUP(2,1/(ABS($AA$41:$AA$161-L42)=MIN(ABS($AA$41:$AA$161-L42))),$AA$41:$AA$161),"—")</f>
-        <v>—</v>
+        <v>470</v>
       </c>
       <c r="Q42" s="78" t="str">
         <f aca="false">IF(ISNUMBER(M42),ROUND(M42*1000,0),"—")</f>
         <v>—</v>
       </c>
-      <c r="R42" s="78" t="str">
+      <c r="R42" s="78" t="n">
         <f aca="false">IF(ISNUMBER(N42),LOOKUP(2,1/(ABS($AA$41:$AA$161-N42)=MIN(ABS($AA$41:$AA$161-N42))),$AA$41:$AA$161),"—")</f>
-        <v>—</v>
+        <v>91</v>
       </c>
       <c r="S42" s="76" t="n">
         <f aca="false">IF(D42="","—",IFERROR((1+ABS(0.05*E16*$C$6/D16)/SQRT(4*$C$6^2+(0.05*E16*$C$6/D16)^2))/(1-ABS(0.05*E16*$C$6/D16)/SQRT(4*$C$6^2+(0.05*E16*$C$6/D16)^2)),"—"))</f>
-        <v>1.01731211570531</v>
+        <v>1.02416978318385</v>
       </c>
       <c r="T42" s="2"/>
       <c r="U42" s="2"/>
@@ -5287,35 +5280,35 @@
       </c>
       <c r="C43" s="53" t="n">
         <f aca="false">C17</f>
-        <v>28</v>
-      </c>
-      <c r="D43" s="71" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" s="71" t="str">
         <f aca="false">D79</f>
-        <v>46.0977222864644</v>
-      </c>
-      <c r="E43" s="72" t="n">
+        <v/>
+      </c>
+      <c r="E43" s="72" t="str">
         <f aca="false">E79</f>
-        <v>12.5288077091515</v>
-      </c>
-      <c r="F43" s="73" t="n">
+        <v/>
+      </c>
+      <c r="F43" s="73" t="str">
         <f aca="false">D60</f>
-        <v>0.948683298050514</v>
-      </c>
-      <c r="G43" s="54" t="n">
+        <v/>
+      </c>
+      <c r="G43" s="54" t="str">
         <f aca="false">E60</f>
-        <v>7</v>
-      </c>
-      <c r="H43" s="74" t="n">
+        <v/>
+      </c>
+      <c r="H43" s="74" t="str">
         <f aca="false">F79</f>
-        <v>1.24828111452191</v>
-      </c>
-      <c r="I43" s="75" t="n">
+        <v/>
+      </c>
+      <c r="I43" s="75" t="str">
         <f aca="false">G79</f>
-        <v>19.1381385238372</v>
-      </c>
-      <c r="J43" s="74" t="n">
+        <v/>
+      </c>
+      <c r="J43" s="74" t="str">
         <f aca="false">I79</f>
-        <v>1.21951219512195</v>
+        <v/>
       </c>
       <c r="K43" s="76" t="str">
         <f aca="false">IF(D43&lt;&gt;"",G133,"—")</f>
@@ -5349,9 +5342,9 @@
         <f aca="false">IF(ISNUMBER(N43),LOOKUP(2,1/(ABS($AA$41:$AA$161-N43)=MIN(ABS($AA$41:$AA$161-N43))),$AA$41:$AA$161),"—")</f>
         <v>—</v>
       </c>
-      <c r="S43" s="76" t="n">
+      <c r="S43" s="76" t="str">
         <f aca="false">IF(D43="","—",IFERROR((1+ABS(0.05*E17*$C$6/D17)/SQRT(4*$C$6^2+(0.05*E17*$C$6/D17)^2))/(1-ABS(0.05*E17*$C$6/D17)/SQRT(4*$C$6^2+(0.05*E17*$C$6/D17)^2)),"—"))</f>
-        <v>1.01117301097261</v>
+        <v>—</v>
       </c>
       <c r="T43" s="2"/>
       <c r="U43" s="2"/>
@@ -6255,27 +6248,27 @@
       </c>
       <c r="D58" s="73" t="n">
         <f aca="false">IF(D15&lt;&gt;"",SQRT(D15/MAX($C$6,0.000000001)),"")</f>
-        <v>1.22474487139159</v>
+        <v>2.85657137141714</v>
       </c>
       <c r="E58" s="54" t="n">
         <f aca="false">IF(D58&lt;&gt;"",MAX(1,ROUND(C10*D58,0)),"")</f>
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="F58" s="54" t="n">
         <f aca="false">IF(E58&lt;&gt;"",E58,"")</f>
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="G58" s="66" t="n">
         <f aca="false">IF(F58&lt;&gt;"",F58*PI()*($C$8+$C$7),"")</f>
-        <v>1441.99102799772</v>
+        <v>3348.93776872672</v>
       </c>
       <c r="H58" s="71" t="n">
         <f aca="false">IF(G58&lt;&gt;"",G58*4*0.00000001724*1000000/(PI()*$C$7^2),"")</f>
-        <v>31.65264</v>
+        <v>73.51136</v>
       </c>
       <c r="I58" s="66" t="n">
         <f aca="false">IF(G58&lt;&gt;"",G58,"")</f>
-        <v>1441.99102799772</v>
+        <v>3348.93776872672</v>
       </c>
       <c r="J58" s="49"/>
       <c r="K58" s="2"/>
@@ -6309,27 +6302,27 @@
       </c>
       <c r="D59" s="73" t="n">
         <f aca="false">IF(D16&lt;&gt;"",SQRT(D16/MAX($C$6,0.000000001)),"")</f>
-        <v>1.15758369027902</v>
+        <v>3.52107937996291</v>
       </c>
       <c r="E59" s="54" t="n">
         <f aca="false">IF(D59&lt;&gt;"",MAX(1,ROUND(C10*D59,0)),"")</f>
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="F59" s="54" t="n">
         <f aca="false">IF(AND(E59&lt;&gt;"",E58&lt;&gt;""),ABS(E59-E58),IF(E59&lt;&gt;"",E59,""))</f>
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G59" s="66" t="n">
         <f aca="false">IF(F59&lt;&gt;"",F59*PI()*($C$8+$C$7),"")</f>
-        <v>160.221225333079</v>
+        <v>772.831792783089</v>
       </c>
       <c r="H59" s="71" t="n">
         <f aca="false">IF(G59&lt;&gt;"",G59*4*0.00000001724*1000000/(PI()*$C$7^2),"")</f>
-        <v>3.51696</v>
+        <v>16.96416</v>
       </c>
       <c r="I59" s="66" t="n">
         <f aca="false">IF(G59&lt;&gt;"",SUM(G58:G59),"")</f>
-        <v>1602.21225333079</v>
+        <v>4121.76956150981</v>
       </c>
       <c r="J59" s="49"/>
       <c r="K59" s="2"/>
@@ -6359,31 +6352,31 @@
       </c>
       <c r="C60" s="53" t="n">
         <f aca="false">C17</f>
-        <v>28</v>
-      </c>
-      <c r="D60" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="D60" s="73" t="str">
         <f aca="false">IF(D17&lt;&gt;"",SQRT(D17/MAX($C$6,0.000000001)),"")</f>
-        <v>0.948683298050514</v>
-      </c>
-      <c r="E60" s="54" t="n">
+        <v/>
+      </c>
+      <c r="E60" s="54" t="str">
         <f aca="false">IF(D60&lt;&gt;"",MAX(1,ROUND(C10*D60,0)),"")</f>
-        <v>7</v>
-      </c>
-      <c r="F60" s="54" t="n">
+        <v/>
+      </c>
+      <c r="F60" s="54" t="str">
         <f aca="false">IF(AND(E60&lt;&gt;"",E59&lt;&gt;""),ABS(E60-E59),IF(E60&lt;&gt;"",E60,""))</f>
-        <v>1</v>
-      </c>
-      <c r="G60" s="66" t="n">
+        <v/>
+      </c>
+      <c r="G60" s="66" t="str">
         <f aca="false">IF(F60&lt;&gt;"",F60*PI()*($C$8+$C$7),"")</f>
-        <v>160.221225333079</v>
-      </c>
-      <c r="H60" s="71" t="n">
+        <v/>
+      </c>
+      <c r="H60" s="71" t="str">
         <f aca="false">IF(G60&lt;&gt;"",G60*4*0.00000001724*1000000/(PI()*$C$7^2),"")</f>
-        <v>3.51696</v>
-      </c>
-      <c r="I60" s="66" t="n">
+        <v/>
+      </c>
+      <c r="I60" s="66" t="str">
         <f aca="false">IF(G60&lt;&gt;"",SUM(G58:G60),"")</f>
-        <v>1762.43347866387</v>
+        <v/>
       </c>
       <c r="J60" s="49"/>
       <c r="K60" s="2"/>
@@ -6878,17 +6871,17 @@
       <c r="D70" s="80"/>
       <c r="E70" s="54" t="n">
         <f aca="false">IFERROR(MAX(E58:E68),"")</f>
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="F70" s="1"/>
       <c r="G70" s="1"/>
       <c r="H70" s="81" t="n">
         <f aca="false">IFERROR(SUM(H58:H68),"")</f>
-        <v>38.68656</v>
+        <v>90.47552</v>
       </c>
       <c r="I70" s="82" t="n">
         <f aca="false">IFERROR(MAX(I58:I68),"")</f>
-        <v>1762.43347866387</v>
+        <v>4121.76956150981</v>
       </c>
       <c r="J70" s="1"/>
       <c r="K70" s="2"/>
@@ -7130,27 +7123,27 @@
       </c>
       <c r="D77" s="71" t="n">
         <f aca="false">IF(AND(ISNUMBER(D15),D15&gt;0),SQRT(D15^2+IF(ISNUMBER(E15),E15,0)^2),"")</f>
-        <v>75.953933407033</v>
+        <v>418.509545888741</v>
       </c>
       <c r="E77" s="72" t="n">
         <f aca="false">IF(AND(ISNUMBER(D15),D15&gt;0),IFERROR(DEGREES(ATAN2(D15,IF(ISNUMBER(E15),E15,0))),""),"")</f>
-        <v>-9.09027692082232</v>
+        <v>12.8673751381485</v>
       </c>
       <c r="F77" s="74" t="n">
         <f aca="false">IF(D77&lt;&gt;"",IFERROR((1+SQRT(((IF(ISNUMBER(D15),D15/MAX((D15/$C$6),0.000000001),C6)-C6)^2+(IF(ISNUMBER(E15),E15/MAX((D15/$C$6),0.000000001),0))^2)/((IF(ISNUMBER(D15),D15/MAX((D15/$C$6),0.000000001),C6)+C6)^2+(IF(ISNUMBER(E15),E15/MAX((D15/$C$6),0.000000001),0))^2)))/(1-SQRT(((IF(ISNUMBER(D15),D15/MAX((D15/$C$6),0.000000001),C6)-C6)^2+(IF(ISNUMBER(E15),E15/MAX((D15/$C$6),0.000000001),0))^2)/((IF(ISNUMBER(D15),D15/MAX((D15/$C$6),0.000000001),C6)+C6)^2+(IF(ISNUMBER(E15),E15/MAX((D15/$C$6),0.000000001),0))^2))),999),"")</f>
-        <v>1.173311183411</v>
+        <v>1.25600695982198</v>
       </c>
       <c r="G77" s="75" t="n">
         <f aca="false">IF(D77&lt;&gt;"",IFERROR(-20*LOG10(MAX(SQRT(((IF(ISNUMBER(D15),D15/MAX((D15/$C$6),0.000000001),C6)-C6)^2+(IF(ISNUMBER(E15),E15/MAX((D15/$C$6),0.000000001),0))^2)/((IF(ISNUMBER(D15),D15/MAX((D15/$C$6),0.000000001),C6)+C6)^2+(IF(ISNUMBER(E15),E15/MAX((D15/$C$6),0.000000001),0))^2)),0.000000001)),0),"")</f>
-        <v>21.9659065411731</v>
+        <v>18.9017732577814</v>
       </c>
       <c r="H77" s="74" t="n">
         <f aca="false">IF(D77&lt;&gt;"",IFERROR(MAX(0,-10*LOG10(1-((IF(ISNUMBER(D15),D15/MAX((D15/$C$6),0.000000001),C6)-C6)^2+(IF(ISNUMBER(E15),E15/MAX((D15/$C$6),0.000000001),0))^2)/((IF(ISNUMBER(D15),D15/MAX((D15/$C$6),0.000000001),C6)+C6)^2+(IF(ISNUMBER(E15),E15/MAX((D15/$C$6),0.000000001),0))^2))),0),"")</f>
-        <v>0.0277062810119371</v>
+        <v>0.056288329783801</v>
       </c>
       <c r="I77" s="74" t="n">
         <f aca="false">IF(D77&lt;&gt;"",IFERROR(((IF(ISNUMBER(D15),D15/MAX((D15/$C$6),0.000000001),C6)-C6)^2+(IF(ISNUMBER(E15),E15/MAX((D15/$C$6),0.000000001),0))^2)/((IF(ISNUMBER(D15),D15/MAX((D15/$C$6),0.000000001),C6)+C6)^2+(IF(ISNUMBER(E15),E15/MAX((D15/$C$6),0.000000001),0))^2)*100,0),"")</f>
-        <v>0.635930047694754</v>
+        <v>1.28772365686098</v>
       </c>
       <c r="J77" s="1"/>
       <c r="K77" s="2"/>
@@ -7184,27 +7177,27 @@
       </c>
       <c r="D78" s="71" t="n">
         <f aca="false">IF(AND(ISNUMBER(D16),D16&gt;0),SQRT(D16^2+IF(ISNUMBER(E16),E16,0)^2),"")</f>
-        <v>70.8378429936994</v>
+        <v>686.987059557893</v>
       </c>
       <c r="E78" s="72" t="n">
         <f aca="false">IF(AND(ISNUMBER(D16),D16&gt;0),IFERROR(DEGREES(ATAN2(D16,IF(ISNUMBER(E16),E16,0))),""),"")</f>
-        <v>18.9465046895091</v>
+        <v>25.5318321834818</v>
       </c>
       <c r="F78" s="74" t="n">
         <f aca="false">IF(D78&lt;&gt;"",IFERROR((1+SQRT(((IF(ISNUMBER(D16),D16/MAX((D16/$C$6),0.000000001),C6)-C6)^2+(IF(ISNUMBER(E16),E16/MAX((D16/$C$6),0.000000001),0))^2)/((IF(ISNUMBER(D16),D16/MAX((D16/$C$6),0.000000001),C6)+C6)^2+(IF(ISNUMBER(E16),E16/MAX((D16/$C$6),0.000000001),0))^2)))/(1-SQRT(((IF(ISNUMBER(D16),D16/MAX((D16/$C$6),0.000000001),C6)-C6)^2+(IF(ISNUMBER(E16),E16/MAX((D16/$C$6),0.000000001),0))^2)/((IF(ISNUMBER(D16),D16/MAX((D16/$C$6),0.000000001),C6)+C6)^2+(IF(ISNUMBER(E16),E16/MAX((D16/$C$6),0.000000001),0))^2))),999),"")</f>
-        <v>1.4072254081761</v>
+        <v>1.60516982405877</v>
       </c>
       <c r="G78" s="75" t="n">
         <f aca="false">IF(D78&lt;&gt;"",IFERROR(-20*LOG10(MAX(SQRT(((IF(ISNUMBER(D16),D16/MAX((D16/$C$6),0.000000001),C6)-C6)^2+(IF(ISNUMBER(E16),E16/MAX((D16/$C$6),0.000000001),0))^2)/((IF(ISNUMBER(D16),D16/MAX((D16/$C$6),0.000000001),C6)+C6)^2+(IF(ISNUMBER(E16),E16/MAX((D16/$C$6),0.000000001),0))^2)),0.000000001)),0),"")</f>
-        <v>15.4336378287394</v>
+        <v>12.6791754929366</v>
       </c>
       <c r="H78" s="74" t="n">
         <f aca="false">IF(D78&lt;&gt;"",IFERROR(MAX(0,-10*LOG10(1-((IF(ISNUMBER(D16),D16/MAX((D16/$C$6),0.000000001),C6)-C6)^2+(IF(ISNUMBER(E16),E16/MAX((D16/$C$6),0.000000001),0))^2)/((IF(ISNUMBER(D16),D16/MAX((D16/$C$6),0.000000001),C6)+C6)^2+(IF(ISNUMBER(E16),E16/MAX((D16/$C$6),0.000000001),0))^2))),0),"")</f>
-        <v>0.126098581795103</v>
+        <v>0.240911000411439</v>
       </c>
       <c r="I78" s="74" t="n">
         <f aca="false">IF(D78&lt;&gt;"",IFERROR(((IF(ISNUMBER(D16),D16/MAX((D16/$C$6),0.000000001),C6)-C6)^2+(IF(ISNUMBER(E16),E16/MAX((D16/$C$6),0.000000001),0))^2)/((IF(ISNUMBER(D16),D16/MAX((D16/$C$6),0.000000001),C6)+C6)^2+(IF(ISNUMBER(E16),E16/MAX((D16/$C$6),0.000000001),0))^2)*100,0),"")</f>
-        <v>2.86177982147687</v>
+        <v>5.39613058204676</v>
       </c>
       <c r="J78" s="1"/>
       <c r="K78" s="2"/>
@@ -7234,31 +7227,31 @@
       </c>
       <c r="C79" s="53" t="n">
         <f aca="false">C17</f>
-        <v>28</v>
-      </c>
-      <c r="D79" s="71" t="n">
+        <v>0</v>
+      </c>
+      <c r="D79" s="71" t="str">
         <f aca="false">IF(AND(ISNUMBER(D17),D17&gt;0),SQRT(D17^2+IF(ISNUMBER(E17),E17,0)^2),"")</f>
-        <v>46.0977222864644</v>
-      </c>
-      <c r="E79" s="72" t="n">
+        <v/>
+      </c>
+      <c r="E79" s="72" t="str">
         <f aca="false">IF(AND(ISNUMBER(D17),D17&gt;0),IFERROR(DEGREES(ATAN2(D17,IF(ISNUMBER(E17),E17,0))),""),"")</f>
-        <v>12.5288077091515</v>
-      </c>
-      <c r="F79" s="74" t="n">
+        <v/>
+      </c>
+      <c r="F79" s="74" t="str">
         <f aca="false">IF(D79&lt;&gt;"",IFERROR((1+SQRT(((IF(ISNUMBER(D17),D17/MAX((D17/$C$6),0.000000001),C6)-C6)^2+(IF(ISNUMBER(E17),E17/MAX((D17/$C$6),0.000000001),0))^2)/((IF(ISNUMBER(D17),D17/MAX((D17/$C$6),0.000000001),C6)+C6)^2+(IF(ISNUMBER(E17),E17/MAX((D17/$C$6),0.000000001),0))^2)))/(1-SQRT(((IF(ISNUMBER(D17),D17/MAX((D17/$C$6),0.000000001),C6)-C6)^2+(IF(ISNUMBER(E17),E17/MAX((D17/$C$6),0.000000001),0))^2)/((IF(ISNUMBER(D17),D17/MAX((D17/$C$6),0.000000001),C6)+C6)^2+(IF(ISNUMBER(E17),E17/MAX((D17/$C$6),0.000000001),0))^2))),999),"")</f>
-        <v>1.24828111452191</v>
-      </c>
-      <c r="G79" s="75" t="n">
+        <v/>
+      </c>
+      <c r="G79" s="75" t="str">
         <f aca="false">IF(D79&lt;&gt;"",IFERROR(-20*LOG10(MAX(SQRT(((IF(ISNUMBER(D17),D17/MAX((D17/$C$6),0.000000001),C6)-C6)^2+(IF(ISNUMBER(E17),E17/MAX((D17/$C$6),0.000000001),0))^2)/((IF(ISNUMBER(D17),D17/MAX((D17/$C$6),0.000000001),C6)+C6)^2+(IF(ISNUMBER(E17),E17/MAX((D17/$C$6),0.000000001),0))^2)),0.000000001)),0),"")</f>
-        <v>19.1381385238372</v>
-      </c>
-      <c r="H79" s="74" t="n">
+        <v/>
+      </c>
+      <c r="H79" s="74" t="str">
         <f aca="false">IF(D79&lt;&gt;"",IFERROR(MAX(0,-10*LOG10(1-((IF(ISNUMBER(D17),D17/MAX((D17/$C$6),0.000000001),C6)-C6)^2+(IF(ISNUMBER(E17),E17/MAX((D17/$C$6),0.000000001),0))^2)/((IF(ISNUMBER(D17),D17/MAX((D17/$C$6),0.000000001),C6)+C6)^2+(IF(ISNUMBER(E17),E17/MAX((D17/$C$6),0.000000001),0))^2))),0),"")</f>
-        <v>0.0532883350506695</v>
-      </c>
-      <c r="I79" s="74" t="n">
+        <v/>
+      </c>
+      <c r="I79" s="74" t="str">
         <f aca="false">IF(D79&lt;&gt;"",IFERROR(((IF(ISNUMBER(D17),D17/MAX((D17/$C$6),0.000000001),C6)-C6)^2+(IF(ISNUMBER(E17),E17/MAX((D17/$C$6),0.000000001),0))^2)/((IF(ISNUMBER(D17),D17/MAX((D17/$C$6),0.000000001),C6)+C6)^2+(IF(ISNUMBER(E17),E17/MAX((D17/$C$6),0.000000001),0))^2)*100,0),"")</f>
-        <v>1.21951219512195</v>
+        <v/>
       </c>
       <c r="J79" s="1"/>
       <c r="K79" s="2"/>
@@ -8215,7 +8208,7 @@
       </c>
       <c r="C103" s="52" t="n">
         <f aca="false">C8</f>
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="D103" s="65" t="s">
         <v>16</v>
@@ -8335,7 +8328,7 @@
       </c>
       <c r="C106" s="53" t="n">
         <f aca="false">IFERROR(IF(E70&lt;&gt;"",VALUE(E70),10),10)</f>
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="D106" s="65" t="s">
         <v>113</v>
@@ -8478,7 +8471,7 @@
       </c>
       <c r="C110" s="67" t="n">
         <f aca="false">IFERROR(IF(C106&gt;0,(C106-1)*C105+C104,""),"")</f>
-        <v>17</v>
+        <v>63</v>
       </c>
       <c r="D110" s="65" t="s">
         <v>16</v>
@@ -8518,7 +8511,7 @@
       </c>
       <c r="C111" s="67" t="n">
         <f aca="false">(C103+C104)/2</f>
-        <v>25.5</v>
+        <v>20.5</v>
       </c>
       <c r="D111" s="65" t="s">
         <v>16</v>
@@ -8558,7 +8551,7 @@
       </c>
       <c r="C112" s="67" t="n">
         <f aca="false">((C103+C104)/2)/25.4</f>
-        <v>1.00393700787402</v>
+        <v>0.807086614173228</v>
       </c>
       <c r="D112" s="65" t="s">
         <v>181</v>
@@ -8598,7 +8591,7 @@
       </c>
       <c r="C113" s="67" t="n">
         <f aca="false">IFERROR(C110/25.4,"")</f>
-        <v>0.669291338582677</v>
+        <v>2.48031496062992</v>
       </c>
       <c r="D113" s="65" t="s">
         <v>181</v>
@@ -8638,7 +8631,7 @@
       </c>
       <c r="C114" s="67" t="n">
         <f aca="false">IFERROR((C112^2*C106^2)/(9*C112+10*C113),"")</f>
-        <v>5.19056793432736</v>
+        <v>20.8009357946279</v>
       </c>
       <c r="D114" s="65" t="s">
         <v>52</v>
@@ -8678,7 +8671,7 @@
       </c>
       <c r="C115" s="67" t="n">
         <f aca="false" t="array" ref="C115:C115">IFERROR(2*PI()*MIN(IF($F$15:$F$25="YES",$C$15:$C$25))*C114,"")</f>
-        <v>233.185096293315</v>
+        <v>934.477359246802</v>
       </c>
       <c r="D115" s="65" t="s">
         <v>9</v>
@@ -9239,31 +9232,31 @@
       </c>
       <c r="D131" s="90" t="n">
         <f aca="false">D15</f>
-        <v>75</v>
+        <v>408</v>
       </c>
       <c r="E131" s="90" t="n">
         <f aca="false">IF(ISNUMBER(E15),E15,"—")</f>
-        <v>-12</v>
+        <v>93.2</v>
       </c>
       <c r="F131" s="90" t="n">
         <f aca="false">IF(ISNUMBER(E77),E77,"—")</f>
-        <v>-9.09027692082232</v>
-      </c>
-      <c r="G131" s="91" t="n">
+        <v>12.8673751381485</v>
+      </c>
+      <c r="G131" s="91" t="str">
         <f aca="false">IFERROR(IF(AND(F15="YES",ISNUMBER(D77),D77&gt;0,ISNUMBER(D15),D15&gt;0),IF(($C$6*IF(ISNUMBER(E15),E15,0)/D15)&lt;0,ABS($C$6*IF(ISNUMBER(E15),E15,0)/D15)/(2*PI()*C15*1000000)*1000000,"—"),"—"),"—")</f>
-        <v>0.178075460802121</v>
-      </c>
-      <c r="H131" s="90" t="str">
+        <v>—</v>
+      </c>
+      <c r="H131" s="90" t="n">
         <f aca="false">IFERROR(IF(AND(F15="YES",ISNUMBER(D77),D77&gt;0,ISNUMBER(D15),D15&gt;0),IF(($C$6*IF(ISNUMBER(E15),E15,0)/D15)&gt;0,1/((2*PI()*C15*1000000)*ABS($C$6*IF(ISNUMBER(E15),E15,0)/D15))*1000000000000,"—"),"—"),"—")</f>
-        <v>—</v>
-      </c>
-      <c r="I131" s="91" t="n">
+        <v>1948.89452809188</v>
+      </c>
+      <c r="I131" s="91" t="str">
         <f aca="false">IFERROR(IF(AND(F15="YES",ISNUMBER(D77),D77&gt;0,ISNUMBER(D15),D15&gt;0),IF((D15*IF(ISNUMBER(E15),E15,0)/($C$6*(D15^2+IF(ISNUMBER(E15),E15,0)^2)))&lt;0,-1/((2*PI()*C15*1000000)*(D15*IF(ISNUMBER(E15),E15,0)/($C$6*(D15^2+IF(ISNUMBER(E15),E15,0)^2))))*1000000,"—"),"—"),"—")</f>
-        <v>7.13414814838496</v>
-      </c>
-      <c r="J131" s="90" t="str">
+        <v>—</v>
+      </c>
+      <c r="J131" s="90" t="n">
         <f aca="false">IFERROR(IF(AND(F15="YES",ISNUMBER(D77),D77&gt;0,ISNUMBER(D15),D15&gt;0),IF((D15*IF(ISNUMBER(E15),E15,0)/($C$6*(D15^2+IF(ISNUMBER(E15),E15,0)^2)))&gt;0,(D15*IF(ISNUMBER(E15),E15,0)/($C$6*(D15^2+IF(ISNUMBER(E15),E15,0)^2)))/(2*PI()*C15*1000000)*1000000000000,"—"),"—"),"—")</f>
-        <v>—</v>
+        <v>96.6516837527188</v>
       </c>
       <c r="K131" s="2"/>
       <c r="L131" s="2"/>
@@ -9296,31 +9289,31 @@
       </c>
       <c r="D132" s="90" t="n">
         <f aca="false">D16</f>
-        <v>67</v>
+        <v>619.9</v>
       </c>
       <c r="E132" s="90" t="n">
         <f aca="false">IF(ISNUMBER(E16),E16,"—")</f>
-        <v>23</v>
+        <v>296.1</v>
       </c>
       <c r="F132" s="90" t="n">
         <f aca="false">IF(ISNUMBER(E78),E78,"—")</f>
-        <v>18.9465046895091</v>
+        <v>25.5318321834818</v>
       </c>
       <c r="G132" s="91" t="str">
         <f aca="false">IFERROR(IF(AND(F16="YES",ISNUMBER(D78),D78&gt;0,ISNUMBER(D16),D16&gt;0),IF(($C$6*IF(ISNUMBER(E16),E16,0)/D16)&lt;0,ABS($C$6*IF(ISNUMBER(E16),E16,0)/D16)/(2*PI()*C16*1000000)*1000000,"—"),"—"),"—")</f>
         <v>—</v>
       </c>
-      <c r="H132" s="90" t="str">
+      <c r="H132" s="90" t="n">
         <f aca="false">IFERROR(IF(AND(F16="YES",ISNUMBER(D78),D78&gt;0,ISNUMBER(D16),D16&gt;0),IF(($C$6*IF(ISNUMBER(E16),E16,0)/D16)&gt;0,1/((2*PI()*C16*1000000)*ABS($C$6*IF(ISNUMBER(E16),E16,0)/D16))*1000000000000,"—"),"—"),"—")</f>
-        <v>—</v>
+        <v>470.287576283575</v>
       </c>
       <c r="I132" s="91" t="str">
         <f aca="false">IFERROR(IF(AND(F16="YES",ISNUMBER(D78),D78&gt;0,ISNUMBER(D16),D16&gt;0),IF((D16*IF(ISNUMBER(E16),E16,0)/($C$6*(D16^2+IF(ISNUMBER(E16),E16,0)^2)))&lt;0,-1/((2*PI()*C16*1000000)*(D16*IF(ISNUMBER(E16),E16,0)/($C$6*(D16^2+IF(ISNUMBER(E16),E16,0)^2))))*1000000,"—"),"—"),"—")</f>
         <v>—</v>
       </c>
-      <c r="J132" s="90" t="str">
+      <c r="J132" s="90" t="n">
         <f aca="false">IFERROR(IF(AND(F16="YES",ISNUMBER(D78),D78&gt;0,ISNUMBER(D16),D16&gt;0),IF((D16*IF(ISNUMBER(E16),E16,0)/($C$6*(D16^2+IF(ISNUMBER(E16),E16,0)^2)))&gt;0,(D16*IF(ISNUMBER(E16),E16,0)/($C$6*(D16^2+IF(ISNUMBER(E16),E16,0)^2)))/(2*PI()*C16*1000000)*1000000000000,"—"),"—"),"—")</f>
-        <v>—</v>
+        <v>87.3661519744635</v>
       </c>
       <c r="K132" s="2"/>
       <c r="L132" s="2"/>
@@ -9349,19 +9342,19 @@
       </c>
       <c r="C133" s="90" t="n">
         <f aca="false">C17</f>
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D133" s="90" t="n">
         <f aca="false">D17</f>
-        <v>45</v>
-      </c>
-      <c r="E133" s="90" t="n">
+        <v>0</v>
+      </c>
+      <c r="E133" s="90" t="str">
         <f aca="false">IF(ISNUMBER(E17),E17,"—")</f>
-        <v>10</v>
-      </c>
-      <c r="F133" s="90" t="n">
+        <v>—</v>
+      </c>
+      <c r="F133" s="90" t="str">
         <f aca="false">IF(ISNUMBER(E79),E79,"—")</f>
-        <v>12.5288077091515</v>
+        <v>—</v>
       </c>
       <c r="G133" s="91" t="str">
         <f aca="false">IFERROR(IF(AND(F17="YES",ISNUMBER(D79),D79&gt;0,ISNUMBER(D17),D17&gt;0),IF(($C$6*IF(ISNUMBER(E17),E17,0)/D17)&lt;0,ABS($C$6*IF(ISNUMBER(E17),E17,0)/D17)/(2*PI()*C17*1000000)*1000000,"—"),"—"),"—")</f>
